--- a/backtest_runs/20260410_193731/by_symbol/JUBS/JUBS.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/JUBS/JUBS.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
         <v>-16906.84</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>156665.08</v>
@@ -863,7 +863,7 @@
         <v>-15212.95999999999</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>141452.12</v>
@@ -909,7 +909,7 @@
         <v>-13678.88</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>127773.24</v>
@@ -955,7 +955,7 @@
         <v>-12304.6</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>115468.64</v>
@@ -1001,7 +1001,7 @@
         <v>-10674.64</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>104794</v>
@@ -1047,7 +1047,7 @@
         <v>-159.8000000000023</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>104634.2</v>
@@ -1093,7 +1093,7 @@
         <v>-6839.440000000001</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>97794.75999999999</v>
@@ -1139,7 +1139,7 @@
         <v>-383.5199999999918</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>97411.24000000001</v>
@@ -1323,7 +1323,7 @@
         <v>-2492.880000000004</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>125599.96</v>
@@ -1369,7 +1369,7 @@
         <v>-6743.559999999999</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>118856.4</v>
@@ -1415,7 +1415,7 @@
         <v>-11122.08000000001</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>107734.32</v>
@@ -1553,7 +1553,7 @@
         <v>-1342.319999999983</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>111889.12</v>
@@ -1599,7 +1599,7 @@
         <v>-1981.520000000015</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K25" s="3" t="n">
         <v>109907.6</v>
@@ -1645,7 +1645,7 @@
         <v>-2141.319999999983</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>107766.28</v>
